--- a/docs/intake/sinistro e assistencias - contatos.xlsx
+++ b/docs/intake/sinistro e assistencias - contatos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ynaa_\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amand\Projetos\AUTOBROKERS RESULTA\AutoBrokers-Fable-Exec-SPEC016\docs\intake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4464AE-5E1F-4FBC-87D1-7C87A5FDD6AF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1720C1D5-3AEF-45D2-A596-0A8AD6FDFFD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C9E79D4-8305-4F37-B8E4-7C2A1FB07606}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{7C9E79D4-8305-4F37-B8E4-7C2A1FB07606}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -162,9 +162,6 @@
     <t>nao tem</t>
   </si>
   <si>
-    <t>08007754035</t>
-  </si>
-  <si>
     <t>30035390 - 2</t>
   </si>
   <si>
@@ -313,6 +310,9 @@
   </si>
   <si>
     <t>um numero para tudo, sem opções na ura</t>
+  </si>
+  <si>
+    <t>11 5502-0700</t>
   </si>
 </sst>
 </file>
@@ -699,21 +699,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BAACE4-F9C1-4B0A-92F0-35EFB4200D7A}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="57.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="33.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="57.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="80" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
@@ -745,15 +745,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>20</v>
@@ -775,7 +775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -792,7 +792,7 @@
         <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>24</v>
@@ -805,7 +805,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -819,7 +819,7 @@
         <v>21</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>25</v>
@@ -832,10 +832,10 @@
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -862,253 +862,253 @@
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="D7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="F8" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="G11" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
